--- a/liens.xlsx
+++ b/liens.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="67">
   <si>
     <t>catégorie</t>
   </si>
@@ -214,6 +214,12 @@
   </si>
   <si>
     <t>drive compresseurs.PNG</t>
+  </si>
+  <si>
+    <t>lock</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -597,17 +603,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="30.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.140625" customWidth="1"/>
+    <col min="5" max="5" width="28.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -623,8 +629,11 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -635,7 +644,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>29</v>
       </c>
@@ -648,7 +657,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -665,7 +674,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -681,8 +690,11 @@
       <c r="E5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
@@ -695,7 +707,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
@@ -706,7 +718,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -720,7 +732,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -734,7 +746,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>45</v>
       </c>
@@ -745,7 +757,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>46</v>
       </c>
@@ -758,7 +770,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>45</v>
       </c>
@@ -775,7 +787,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>45</v>
       </c>
@@ -788,7 +800,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>45</v>
       </c>
@@ -805,7 +817,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>45</v>
       </c>
@@ -819,7 +831,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>30</v>
       </c>
@@ -830,7 +842,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>30</v>
       </c>
@@ -843,7 +855,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>30</v>
       </c>
@@ -860,7 +872,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -876,8 +888,11 @@
       <c r="E19" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>30</v>
       </c>
@@ -890,7 +905,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -907,7 +922,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -921,7 +936,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>27</v>
       </c>
@@ -932,7 +947,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -946,7 +961,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>

--- a/liens.xlsx
+++ b/liens.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="70">
   <si>
     <t>catégorie</t>
   </si>
@@ -220,6 +220,15 @@
   </si>
   <si>
     <t>x</t>
+  </si>
+  <si>
+    <t>Dieppe</t>
+  </si>
+  <si>
+    <t>Port de plaisance</t>
+  </si>
+  <si>
+    <t>https://portdedieppe.fr/le-port-de-plaisance/</t>
   </si>
 </sst>
 </file>
@@ -603,13 +612,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23" style="1" customWidth="1"/>
+    <col min="4" max="4" width="88.42578125" style="1" customWidth="1"/>
     <col min="5" max="5" width="28.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -832,44 +841,42 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="A16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="5" t="s">
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B18" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="8" t="s">
+      <c r="C18" s="6"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="8" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -879,47 +886,47 @@
       <c r="B19" t="s">
         <v>26</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" t="s">
         <v>58</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F20" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B21" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="2" t="s">
+      <c r="C21" s="6"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="2" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -929,36 +936,39 @@
       <c r="B22" t="s">
         <v>44</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D23" s="9" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="5" t="s">
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="5" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" t="s">
-        <v>49</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -966,12 +976,26 @@
         <v>27</v>
       </c>
       <c r="C25" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" t="s">
         <v>51</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="D26" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>53</v>
       </c>
     </row>
@@ -985,23 +1009,24 @@
     <hyperlink ref="E9" r:id="rId6"/>
     <hyperlink ref="E10" r:id="rId7"/>
     <hyperlink ref="E11" r:id="rId8"/>
-    <hyperlink ref="E20" r:id="rId9"/>
-    <hyperlink ref="E23" r:id="rId10"/>
-    <hyperlink ref="E24" r:id="rId11"/>
+    <hyperlink ref="E21" r:id="rId9"/>
+    <hyperlink ref="E24" r:id="rId10"/>
+    <hyperlink ref="E25" r:id="rId11"/>
     <hyperlink ref="E2" r:id="rId12"/>
-    <hyperlink ref="E16" r:id="rId13"/>
+    <hyperlink ref="E17" r:id="rId13"/>
     <hyperlink ref="E14" r:id="rId14"/>
     <hyperlink ref="E12" r:id="rId15"/>
     <hyperlink ref="E13" r:id="rId16"/>
-    <hyperlink ref="D25" r:id="rId17"/>
-    <hyperlink ref="E25" r:id="rId18"/>
-    <hyperlink ref="E17" r:id="rId19"/>
-    <hyperlink ref="E18" r:id="rId20"/>
-    <hyperlink ref="E19" r:id="rId21"/>
-    <hyperlink ref="D22" r:id="rId22"/>
-    <hyperlink ref="E21" r:id="rId23"/>
+    <hyperlink ref="D26" r:id="rId17"/>
+    <hyperlink ref="E26" r:id="rId18"/>
+    <hyperlink ref="E18" r:id="rId19"/>
+    <hyperlink ref="E19" r:id="rId20"/>
+    <hyperlink ref="E20" r:id="rId21"/>
+    <hyperlink ref="D23" r:id="rId22"/>
+    <hyperlink ref="E22" r:id="rId23"/>
+    <hyperlink ref="D16" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId24"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId25"/>
 </worksheet>
 </file>
--- a/liens.xlsx
+++ b/liens.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="82">
   <si>
     <t>catégorie</t>
   </si>
@@ -36,30 +36,9 @@
     <t>image</t>
   </si>
   <si>
-    <t>Formation</t>
-  </si>
-  <si>
     <t>N1</t>
   </si>
   <si>
-    <t>calendrier de présence moniteur</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/drive/u/0/folders/1rFJEf7VlS9QoiBME4AcHEi4efEqHQ7ms</t>
-  </si>
-  <si>
-    <t>calendrier_presence.png</t>
-  </si>
-  <si>
-    <t>fichie de suivi N1</t>
-  </si>
-  <si>
-    <t>https://notebooklm.google.com/notebook/abd26236-a7dc-4906-a4a4-02ed93e42ce4</t>
-  </si>
-  <si>
-    <t>suivi_n1.png</t>
-  </si>
-  <si>
     <t>FFESSM</t>
   </si>
   <si>
@@ -81,9 +60,6 @@
     <t>inscription Glénan</t>
   </si>
   <si>
-    <t>https://association-sportive-de-sorbonne-sim.assoconnect.com/collect/description/715905-y-stage-de-giens-ete-2026</t>
-  </si>
-  <si>
     <t>https://association-sportive-de-sorbonne-sim.assoconnect.com/collect/description/722164-p-we-de-marseille-frioul-sept-2026</t>
   </si>
   <si>
@@ -108,9 +84,6 @@
     <t>https://drive.google.com/drive/u/1/folders/1b-r6p9-zRpVgKEELuy3HgH2cavWhQZeX</t>
   </si>
   <si>
-    <t xml:space="preserve">Formation </t>
-  </si>
-  <si>
     <t>Matériel</t>
   </si>
   <si>
@@ -229,13 +202,76 @@
   </si>
   <si>
     <t>https://portdedieppe.fr/le-port-de-plaisance/</t>
+  </si>
+  <si>
+    <t>https://association-sportive-de-sorbonne-sim.assoconnect.com/collect/description/727470-e-stage-archipel-des-glenan-12-16-septembre-2026</t>
+  </si>
+  <si>
+    <t>https://forms.gle/UqSzMYsF4ZXwTW9r5</t>
+  </si>
+  <si>
+    <t>fichier info</t>
+  </si>
+  <si>
+    <t>Formations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formations </t>
+  </si>
+  <si>
+    <t>Poulpoquizz</t>
+  </si>
+  <si>
+    <t>Initiateurs</t>
+  </si>
+  <si>
+    <t>Drive initiateurs</t>
+  </si>
+  <si>
+    <t>Drive PN2</t>
+  </si>
+  <si>
+    <t>Drive PN1</t>
+  </si>
+  <si>
+    <t>Lien vers le MFT FFESSM</t>
+  </si>
+  <si>
+    <t>https://plongee.ffessm.fr/mft</t>
+  </si>
+  <si>
+    <t>MFT FFESSM.PNG</t>
+  </si>
+  <si>
+    <t>Présence Piscine</t>
+  </si>
+  <si>
+    <t>https://beta.framadate.org/polls/1a183f9381edea424a43</t>
+  </si>
+  <si>
+    <t>piscine_JT.jpg</t>
+  </si>
+  <si>
+    <t>drive.PNG</t>
+  </si>
+  <si>
+    <t>initiateur.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1Khd16aOr3tb0SGSDaf-LFWPqbObfNjbp?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/12jL9kPcY0IK_BNcxE-p-XPvNIG3ZnR2b?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1LFzezVLM0atpdnad_aEQJvTLsRhrpkqf?usp=sharing</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -247,6 +283,14 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -285,7 +329,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment shrinkToFit="1"/>
@@ -309,6 +353,15 @@
       <alignment shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -612,421 +665,518 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="30.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="88.42578125" style="1" customWidth="1"/>
     <col min="5" max="5" width="28.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>65</v>
+      <c r="F1" s="13" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>5</v>
+      <c r="A2" s="15" t="s">
+        <v>64</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="4"/>
       <c r="E2" s="5" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="A3" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="8" t="s">
-        <v>39</v>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="8" t="s">
-        <v>22</v>
+      <c r="A13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>50</v>
+      <c r="A14" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>34</v>
+      <c r="A15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="6"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="8" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16" s="2"/>
+        <v>61</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="A17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>30</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="5" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="7"/>
       <c r="E18" s="8" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>57</v>
+        <v>38</v>
+      </c>
+      <c r="C19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" t="s">
         <v>58</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="C21" t="s">
         <v>59</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="D21" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="F20" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="2" t="s">
-        <v>40</v>
-      </c>
+      <c r="E21" s="2"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>30</v>
-      </c>
-      <c r="B22" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>64</v>
+      <c r="A22" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" t="s">
-        <v>35</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>61</v>
+      <c r="A23" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="6"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="8" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="5" t="s">
-        <v>41</v>
+      <c r="A24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>21</v>
+      </c>
+      <c r="B25" t="s">
+        <v>18</v>
       </c>
       <c r="C25" t="s">
         <v>49</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="E25" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F25" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="6"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" t="s">
-        <v>51</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>53</v>
+      <c r="D31" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E7" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E6" r:id="rId3"/>
-    <hyperlink ref="E15" r:id="rId4"/>
-    <hyperlink ref="E8" r:id="rId5"/>
-    <hyperlink ref="E9" r:id="rId6"/>
-    <hyperlink ref="E10" r:id="rId7"/>
-    <hyperlink ref="E11" r:id="rId8"/>
-    <hyperlink ref="E21" r:id="rId9"/>
-    <hyperlink ref="E24" r:id="rId10"/>
-    <hyperlink ref="E25" r:id="rId11"/>
+    <hyperlink ref="E11" r:id="rId1"/>
+    <hyperlink ref="E4" r:id="rId2"/>
+    <hyperlink ref="E7" r:id="rId3"/>
+    <hyperlink ref="E20" r:id="rId4"/>
+    <hyperlink ref="E12" r:id="rId5"/>
+    <hyperlink ref="E13" r:id="rId6"/>
+    <hyperlink ref="E14" r:id="rId7"/>
+    <hyperlink ref="E15" r:id="rId8"/>
+    <hyperlink ref="E26" r:id="rId9"/>
+    <hyperlink ref="E29" r:id="rId10"/>
+    <hyperlink ref="E30" r:id="rId11"/>
     <hyperlink ref="E2" r:id="rId12"/>
-    <hyperlink ref="E17" r:id="rId13"/>
-    <hyperlink ref="E14" r:id="rId14"/>
-    <hyperlink ref="E12" r:id="rId15"/>
-    <hyperlink ref="E13" r:id="rId16"/>
-    <hyperlink ref="D26" r:id="rId17"/>
-    <hyperlink ref="E26" r:id="rId18"/>
-    <hyperlink ref="E18" r:id="rId19"/>
-    <hyperlink ref="E19" r:id="rId20"/>
-    <hyperlink ref="E20" r:id="rId21"/>
-    <hyperlink ref="D23" r:id="rId22"/>
-    <hyperlink ref="E22" r:id="rId23"/>
-    <hyperlink ref="D16" r:id="rId24"/>
+    <hyperlink ref="E22" r:id="rId13"/>
+    <hyperlink ref="E19" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E18" r:id="rId16"/>
+    <hyperlink ref="D31" r:id="rId17"/>
+    <hyperlink ref="E31" r:id="rId18"/>
+    <hyperlink ref="E23" r:id="rId19"/>
+    <hyperlink ref="E24" r:id="rId20"/>
+    <hyperlink ref="E25" r:id="rId21"/>
+    <hyperlink ref="D28" r:id="rId22"/>
+    <hyperlink ref="E27" r:id="rId23"/>
+    <hyperlink ref="D21" r:id="rId24"/>
+    <hyperlink ref="D20" r:id="rId25" location="gid=0"/>
+    <hyperlink ref="D16" r:id="rId26"/>
+    <hyperlink ref="D17" r:id="rId27"/>
+    <hyperlink ref="E17" r:id="rId28"/>
+    <hyperlink ref="D3" r:id="rId29"/>
+    <hyperlink ref="E3" r:id="rId30"/>
+    <hyperlink ref="D5" r:id="rId31"/>
+    <hyperlink ref="E5" r:id="rId32"/>
+    <hyperlink ref="E6" r:id="rId33"/>
+    <hyperlink ref="E8" r:id="rId34"/>
+    <hyperlink ref="E10" r:id="rId35"/>
+    <hyperlink ref="E9" r:id="rId36"/>
+    <hyperlink ref="D10" r:id="rId37"/>
+    <hyperlink ref="D6" r:id="rId38"/>
+    <hyperlink ref="D8" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId25"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId40"/>
 </worksheet>
 </file>
--- a/liens.xlsx
+++ b/liens.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="83">
   <si>
     <t>catégorie</t>
   </si>
@@ -265,6 +265,9 @@
   </si>
   <si>
     <t>https://drive.google.com/drive/folders/1LFzezVLM0atpdnad_aEQJvTLsRhrpkqf?usp=sharing</t>
+  </si>
+  <si>
+    <t>port de Dieppe.jfif</t>
   </si>
 </sst>
 </file>
@@ -980,7 +983,9 @@
       <c r="D21" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E21" s="2"/>
+      <c r="E21" s="2" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
@@ -1175,8 +1180,9 @@
     <hyperlink ref="D10" r:id="rId37"/>
     <hyperlink ref="D6" r:id="rId38"/>
     <hyperlink ref="D8" r:id="rId39"/>
+    <hyperlink ref="E21" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId40"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId41"/>
 </worksheet>
 </file>